--- a/files/subject.xlsx
+++ b/files/subject.xlsx
@@ -440,12 +440,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>subject_code</t>
+          <t>subjectcode</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>subject_name</t>
+          <t>subjectname</t>
         </is>
       </c>
     </row>
